--- a/employee_surveys/007_team_role_ownership_survey--employee_surveys.xlsx
+++ b/employee_surveys/007_team_role_ownership_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
